--- a/Docs/QA-Testing/Test_Case_DecisionTable.xlsx
+++ b/Docs/QA-Testing/Test_Case_DecisionTable.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\task1sp4\sc63\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\KiemChungPhanMem\Docs\QA-Testing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0F0F6A5-0E80-431E-B2E3-D0E2E288BE2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2C9F1F4-CD03-4268-B51F-67F470E1C921}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1018,18 +1018,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1047,6 +1035,18 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1359,15 +1359,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15.6" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="23" t="s">
         <v>91</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="2"/>
@@ -1379,36 +1379,36 @@
       <c r="G2" s="2"/>
     </row>
     <row r="3" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="22" t="s">
         <v>94</v>
       </c>
-      <c r="B3" s="16"/>
+      <c r="B3" s="22"/>
     </row>
     <row r="4" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="B4" s="15"/>
-      <c r="C4" s="15"/>
-      <c r="D4" s="15"/>
-      <c r="E4" s="15"/>
+      <c r="B4" s="21"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
     </row>
     <row r="5" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="B5" s="15"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="15"/>
-      <c r="E5" s="15"/>
+      <c r="B5" s="21"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="21"/>
     </row>
     <row r="6" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="21" t="s">
         <v>95</v>
       </c>
-      <c r="B6" s="15"/>
-      <c r="C6" s="15"/>
-      <c r="D6" s="15"/>
+      <c r="B6" s="21"/>
+      <c r="C6" s="21"/>
+      <c r="D6" s="21"/>
     </row>
     <row r="7" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="11"/>
@@ -1417,107 +1417,112 @@
       <c r="D7" s="11"/>
     </row>
     <row r="8" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="16" t="s">
+      <c r="A8" s="22" t="s">
         <v>97</v>
       </c>
-      <c r="B8" s="16"/>
-      <c r="C8" s="16"/>
+      <c r="B8" s="22"/>
+      <c r="C8" s="22"/>
     </row>
     <row r="9" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="15" t="s">
+      <c r="A9" s="21" t="s">
         <v>98</v>
       </c>
-      <c r="B9" s="15"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="15"/>
-      <c r="E9" s="15"/>
-      <c r="F9" s="15"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="21"/>
+      <c r="D9" s="21"/>
+      <c r="E9" s="21"/>
+      <c r="F9" s="21"/>
     </row>
     <row r="10" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="15" t="s">
+      <c r="A10" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="B10" s="15"/>
-      <c r="C10" s="15"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
     </row>
     <row r="11" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="15" t="s">
+      <c r="A11" s="21" t="s">
         <v>100</v>
       </c>
-      <c r="B11" s="15"/>
-      <c r="C11" s="15"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="21"/>
     </row>
     <row r="12" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="15" t="s">
+      <c r="A12" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="B12" s="15"/>
-      <c r="C12" s="15"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="15"/>
-      <c r="G12" s="15"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="21"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="21"/>
+      <c r="F12" s="21"/>
+      <c r="G12" s="21"/>
     </row>
     <row r="13" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="15" t="s">
+      <c r="A13" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="B13" s="15"/>
-      <c r="C13" s="15"/>
-      <c r="D13" s="15"/>
-      <c r="E13" s="15"/>
-      <c r="F13" s="15"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="21"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="21"/>
     </row>
     <row r="14" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="15" t="s">
+      <c r="A14" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="B14" s="15"/>
-      <c r="C14" s="15"/>
-      <c r="D14" s="15"/>
-      <c r="E14" s="15"/>
-      <c r="F14" s="15"/>
+      <c r="B14" s="21"/>
+      <c r="C14" s="21"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
     </row>
     <row r="15" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15"/>
     </row>
     <row r="16" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="15" t="s">
+      <c r="A16" s="21" t="s">
         <v>92</v>
       </c>
-      <c r="B16" s="15"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="15"/>
-      <c r="I16" s="15"/>
+      <c r="B16" s="21"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="21"/>
+      <c r="F16" s="21"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="21"/>
+      <c r="I16" s="21"/>
     </row>
     <row r="17" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A17" s="15" t="s">
+      <c r="A17" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="B17" s="15"/>
-      <c r="C17" s="15"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="15"/>
-      <c r="G17" s="15"/>
+      <c r="B17" s="21"/>
+      <c r="C17" s="21"/>
+      <c r="D17" s="21"/>
+      <c r="E17" s="21"/>
+      <c r="F17" s="21"/>
+      <c r="G17" s="21"/>
     </row>
     <row r="18" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A18" s="15" t="s">
+      <c r="A18" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="B18" s="15"/>
-      <c r="C18" s="15"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="15"/>
+      <c r="B18" s="21"/>
+      <c r="C18" s="21"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="21"/>
+      <c r="G18" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A3:B3"/>
     <mergeCell ref="A9:F9"/>
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A16:I16"/>
@@ -1528,11 +1533,6 @@
     <mergeCell ref="A12:G12"/>
     <mergeCell ref="A11:C11"/>
     <mergeCell ref="A10:C10"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A6:D6"/>
-    <mergeCell ref="A5:E5"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="A3:B3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" copies="0" r:id="rId1"/>
@@ -1594,7 +1594,7 @@
       <c r="K2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="17" t="s">
+      <c r="L2" s="13" t="s">
         <v>207</v>
       </c>
     </row>
@@ -1761,7 +1761,7 @@
       <c r="K7" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="L7" s="17" t="s">
+      <c r="L7" s="13" t="s">
         <v>211</v>
       </c>
     </row>
@@ -1835,14 +1835,14 @@
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" s="18" t="s">
+      <c r="A11" s="14" t="s">
         <v>197</v>
       </c>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" s="4"/>
@@ -1861,7 +1861,7 @@
       <c r="F12" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="L12" s="17" t="s">
+      <c r="L12" s="13" t="s">
         <v>212</v>
       </c>
     </row>
@@ -1985,7 +1985,7 @@
       </c>
     </row>
     <row r="19" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A19" s="19" t="s">
+      <c r="A19" s="15" t="s">
         <v>11</v>
       </c>
       <c r="B19" s="6" t="s">
@@ -2027,7 +2027,7 @@
       <c r="A1" t="s">
         <v>216</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="E1" s="13" t="s">
         <v>207</v>
       </c>
     </row>
@@ -2103,7 +2103,7 @@
         <v>14</v>
       </c>
       <c r="D6" s="7"/>
-      <c r="E6" s="17" t="s">
+      <c r="E6" s="13" t="s">
         <v>211</v>
       </c>
     </row>
@@ -2143,7 +2143,7 @@
       <c r="D9" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="E9" s="17" t="s">
+      <c r="E9" s="13" t="s">
         <v>212</v>
       </c>
     </row>
@@ -2330,7 +2330,7 @@
       <c r="J2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="17" t="s">
+      <c r="K2" s="13" t="s">
         <v>207</v>
       </c>
     </row>
@@ -2515,7 +2515,7 @@
       <c r="H8" s="7"/>
       <c r="I8" s="7"/>
       <c r="J8" s="7"/>
-      <c r="K8" s="17" t="s">
+      <c r="K8" s="13" t="s">
         <v>211</v>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="K11" s="17" t="s">
+      <c r="K11" s="13" t="s">
         <v>212</v>
       </c>
     </row>
@@ -2750,7 +2750,7 @@
       </c>
     </row>
     <row r="22" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A22" s="19" t="s">
+      <c r="A22" s="15" t="s">
         <v>11</v>
       </c>
       <c r="B22" s="6" t="s">
@@ -2813,7 +2813,7 @@
       <c r="G2" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="H2" s="17" t="s">
+      <c r="H2" s="13" t="s">
         <v>207</v>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       <c r="G7" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="H7" s="17" t="s">
+      <c r="H7" s="13" t="s">
         <v>211</v>
       </c>
     </row>
@@ -2962,7 +2962,7 @@
       <c r="A10" t="s">
         <v>217</v>
       </c>
-      <c r="H10" s="17" t="s">
+      <c r="H10" s="13" t="s">
         <v>212</v>
       </c>
     </row>
@@ -2994,7 +2994,7 @@
       <c r="D12" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="H12" s="20"/>
+      <c r="H12" s="16"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="9" t="s">
@@ -3009,7 +3009,7 @@
       <c r="D13" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="H13" s="20" t="s">
+      <c r="H13" s="16" t="s">
         <v>244</v>
       </c>
     </row>
@@ -3101,1157 +3101,1157 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="A1" s="21" t="s">
+      <c r="A1" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="21" t="s">
+      <c r="B1" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="C1" s="17" t="s">
         <v>151</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="E1" s="21" t="s">
+      <c r="E1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="F1" s="21" t="s">
+      <c r="F1" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="21" t="s">
+      <c r="G1" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="H1" s="21" t="s">
+      <c r="H1" s="17" t="s">
         <v>245</v>
       </c>
-      <c r="I1" s="21" t="s">
+      <c r="I1" s="17" t="s">
         <v>246</v>
       </c>
-      <c r="J1" s="21" t="s">
+      <c r="J1" s="17" t="s">
         <v>247</v>
       </c>
-      <c r="K1" s="21" t="s">
+      <c r="K1" s="17" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="45" x14ac:dyDescent="0.3">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="18" t="s">
         <v>152</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="C2" s="18" t="s">
         <v>153</v>
       </c>
-      <c r="D2" s="22" t="s">
+      <c r="D2" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="E2" s="22" t="s">
+      <c r="E2" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="22" t="s">
+      <c r="F2" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="G2" s="22" t="s">
+      <c r="G2" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="H2" s="22" t="s">
+      <c r="H2" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="I2" s="22">
+      <c r="I2" s="18">
         <v>200</v>
       </c>
-      <c r="J2" s="22">
+      <c r="J2" s="18">
         <v>200</v>
       </c>
-      <c r="K2" s="24" t="s">
+      <c r="K2" s="20" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="30" x14ac:dyDescent="0.3">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="B3" s="22" t="s">
+      <c r="B3" s="18" t="s">
         <v>154</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="18" t="s">
         <v>155</v>
       </c>
-      <c r="D3" s="22" t="s">
+      <c r="D3" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="E3" s="22" t="s">
+      <c r="E3" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="F3" s="22" t="s">
+      <c r="F3" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="22" t="s">
+      <c r="G3" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="H3" s="22" t="s">
+      <c r="H3" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="I3" s="22">
+      <c r="I3" s="18">
         <v>401</v>
       </c>
-      <c r="J3" s="22">
+      <c r="J3" s="18">
         <v>401</v>
       </c>
-      <c r="K3" s="24" t="s">
+      <c r="K3" s="20" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="60" x14ac:dyDescent="0.3">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="18" t="s">
         <v>248</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="C4" s="18" t="s">
         <v>156</v>
       </c>
-      <c r="D4" s="22" t="s">
+      <c r="D4" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="E4" s="22" t="s">
+      <c r="E4" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="F4" s="22" t="s">
+      <c r="F4" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="22" t="s">
+      <c r="G4" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="H4" s="22" t="s">
+      <c r="H4" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="I4" s="22">
+      <c r="I4" s="18">
         <v>401</v>
       </c>
-      <c r="J4" s="22">
+      <c r="J4" s="18">
         <v>401</v>
       </c>
-      <c r="K4" s="24" t="s">
+      <c r="K4" s="20" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="30" x14ac:dyDescent="0.3">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="18" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="22" t="s">
+      <c r="B5" s="18" t="s">
         <v>157</v>
       </c>
-      <c r="C5" s="22" t="s">
+      <c r="C5" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="D5" s="22" t="s">
+      <c r="D5" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="E5" s="22" t="s">
+      <c r="E5" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="F5" s="22" t="s">
+      <c r="F5" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="G5" s="22" t="s">
+      <c r="G5" s="18" t="s">
         <v>50</v>
       </c>
-      <c r="H5" s="22" t="s">
+      <c r="H5" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="I5" s="22">
+      <c r="I5" s="18">
         <v>200</v>
       </c>
-      <c r="J5" s="22">
+      <c r="J5" s="18">
         <v>200</v>
       </c>
-      <c r="K5" s="24" t="s">
+      <c r="K5" s="20" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="45" x14ac:dyDescent="0.3">
-      <c r="A6" s="22" t="s">
+      <c r="A6" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="18" t="s">
         <v>158</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="C6" s="18" t="s">
         <v>159</v>
       </c>
-      <c r="D6" s="22" t="s">
+      <c r="D6" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="22" t="s">
+      <c r="E6" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="F6" s="22" t="s">
+      <c r="F6" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="22" t="s">
+      <c r="G6" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="H6" s="22" t="s">
+      <c r="H6" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="I6" s="22">
+      <c r="I6" s="18">
         <v>200</v>
       </c>
-      <c r="J6" s="22">
+      <c r="J6" s="18">
         <v>200</v>
       </c>
-      <c r="K6" s="24" t="s">
+      <c r="K6" s="20" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="75" x14ac:dyDescent="0.3">
-      <c r="A7" s="22" t="s">
+      <c r="A7" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="B7" s="22" t="s">
+      <c r="B7" s="18" t="s">
         <v>160</v>
       </c>
-      <c r="C7" s="22" t="s">
+      <c r="C7" s="18" t="s">
         <v>161</v>
       </c>
-      <c r="D7" s="22" t="s">
+      <c r="D7" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="22" t="s">
+      <c r="E7" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="F7" s="22" t="s">
+      <c r="F7" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="G7" s="22" t="s">
+      <c r="G7" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="H7" s="22" t="s">
+      <c r="H7" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="I7" s="22">
+      <c r="I7" s="18">
         <v>403</v>
       </c>
-      <c r="J7" s="22">
+      <c r="J7" s="18">
         <v>403</v>
       </c>
-      <c r="K7" s="24" t="s">
+      <c r="K7" s="20" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="45" x14ac:dyDescent="0.3">
-      <c r="A8" s="22" t="s">
+      <c r="A8" s="18" t="s">
         <v>55</v>
       </c>
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="C8" s="22" t="s">
+      <c r="C8" s="18" t="s">
         <v>163</v>
       </c>
-      <c r="D8" s="22" t="s">
+      <c r="D8" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="22" t="s">
+      <c r="E8" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="F8" s="22" t="s">
+      <c r="F8" s="18" t="s">
         <v>56</v>
       </c>
-      <c r="G8" s="22" t="s">
+      <c r="G8" s="18" t="s">
         <v>57</v>
       </c>
-      <c r="H8" s="22" t="s">
+      <c r="H8" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="I8" s="22">
+      <c r="I8" s="18">
         <v>200</v>
       </c>
-      <c r="J8" s="22">
+      <c r="J8" s="18">
         <v>200</v>
       </c>
-      <c r="K8" s="24" t="s">
+      <c r="K8" s="20" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="45" x14ac:dyDescent="0.3">
-      <c r="A9" s="22" t="s">
+      <c r="A9" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="B9" s="22" t="s">
+      <c r="B9" s="18" t="s">
         <v>162</v>
       </c>
-      <c r="C9" s="22" t="s">
+      <c r="C9" s="18" t="s">
         <v>164</v>
       </c>
-      <c r="D9" s="22" t="s">
+      <c r="D9" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="E9" s="22" t="s">
+      <c r="E9" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="F9" s="22" t="s">
+      <c r="F9" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="G9" s="22" t="s">
+      <c r="G9" s="18" t="s">
         <v>59</v>
       </c>
-      <c r="H9" s="22" t="s">
+      <c r="H9" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="I9" s="22">
+      <c r="I9" s="18">
         <v>200</v>
       </c>
-      <c r="J9" s="22">
+      <c r="J9" s="18">
         <v>200</v>
       </c>
-      <c r="K9" s="24" t="s">
+      <c r="K9" s="20" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="60" x14ac:dyDescent="0.3">
-      <c r="A10" s="22" t="s">
+      <c r="A10" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="18" t="s">
         <v>165</v>
       </c>
-      <c r="C10" s="22" t="s">
+      <c r="C10" s="18" t="s">
         <v>166</v>
       </c>
-      <c r="D10" s="22" t="s">
+      <c r="D10" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="E10" s="22" t="s">
+      <c r="E10" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="F10" s="22" t="s">
+      <c r="F10" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="G10" s="22" t="s">
+      <c r="G10" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="H10" s="22" t="s">
+      <c r="H10" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="I10" s="22">
+      <c r="I10" s="18">
         <v>200</v>
       </c>
-      <c r="J10" s="22">
+      <c r="J10" s="18">
         <v>200</v>
       </c>
-      <c r="K10" s="24" t="s">
+      <c r="K10" s="20" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="60" x14ac:dyDescent="0.3">
-      <c r="A11" s="22" t="s">
+      <c r="A11" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="B11" s="22" t="s">
+      <c r="B11" s="18" t="s">
         <v>167</v>
       </c>
-      <c r="C11" s="22" t="s">
+      <c r="C11" s="18" t="s">
         <v>168</v>
       </c>
-      <c r="D11" s="22" t="s">
+      <c r="D11" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="E11" s="22" t="s">
+      <c r="E11" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="F11" s="22" t="s">
+      <c r="F11" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="G11" s="22" t="s">
+      <c r="G11" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="H11" s="22" t="s">
+      <c r="H11" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="I11" s="22">
+      <c r="I11" s="18">
         <v>401</v>
       </c>
-      <c r="J11" s="22">
+      <c r="J11" s="18">
         <v>401</v>
       </c>
-      <c r="K11" s="24" t="s">
+      <c r="K11" s="20" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="75" x14ac:dyDescent="0.3">
-      <c r="A12" s="22" t="s">
+      <c r="A12" s="18" t="s">
         <v>64</v>
       </c>
-      <c r="B12" s="22" t="s">
+      <c r="B12" s="18" t="s">
         <v>250</v>
       </c>
-      <c r="C12" s="22" t="s">
+      <c r="C12" s="18" t="s">
         <v>169</v>
       </c>
-      <c r="D12" s="22" t="s">
+      <c r="D12" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="E12" s="22" t="s">
+      <c r="E12" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="F12" s="22" t="s">
+      <c r="F12" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="G12" s="22" t="s">
+      <c r="G12" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="H12" s="22" t="s">
+      <c r="H12" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="I12" s="22">
+      <c r="I12" s="18">
         <v>403</v>
       </c>
-      <c r="J12" s="22">
+      <c r="J12" s="18">
         <v>403</v>
       </c>
-      <c r="K12" s="24" t="s">
+      <c r="K12" s="20" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="90" x14ac:dyDescent="0.3">
-      <c r="A13" s="22" t="s">
+      <c r="A13" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="B13" s="22" t="s">
+      <c r="B13" s="18" t="s">
         <v>170</v>
       </c>
-      <c r="C13" s="22" t="s">
+      <c r="C13" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="D13" s="22" t="s">
+      <c r="D13" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="E13" s="22" t="s">
+      <c r="E13" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="F13" s="22" t="s">
+      <c r="F13" s="18" t="s">
         <v>251</v>
       </c>
-      <c r="G13" s="22" t="s">
+      <c r="G13" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="H13" s="22" t="s">
+      <c r="H13" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="I13" s="22">
+      <c r="I13" s="18">
         <v>200</v>
       </c>
-      <c r="J13" s="22">
+      <c r="J13" s="18">
         <v>200</v>
       </c>
-      <c r="K13" s="24" t="s">
+      <c r="K13" s="20" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="75" x14ac:dyDescent="0.3">
-      <c r="A14" s="22" t="s">
+      <c r="A14" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="B14" s="22" t="s">
+      <c r="B14" s="18" t="s">
         <v>165</v>
       </c>
-      <c r="C14" s="22" t="s">
+      <c r="C14" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="D14" s="22" t="s">
+      <c r="D14" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="E14" s="22" t="s">
+      <c r="E14" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="F14" s="22" t="s">
+      <c r="F14" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="G14" s="22" t="s">
+      <c r="G14" s="18" t="s">
         <v>70</v>
       </c>
-      <c r="H14" s="22" t="s">
+      <c r="H14" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="I14" s="22">
+      <c r="I14" s="18">
         <v>200</v>
       </c>
-      <c r="J14" s="22">
+      <c r="J14" s="18">
         <v>200</v>
       </c>
-      <c r="K14" s="24" t="s">
+      <c r="K14" s="20" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="75" x14ac:dyDescent="0.3">
-      <c r="A15" s="22" t="s">
+      <c r="A15" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="B15" s="22" t="s">
+      <c r="B15" s="18" t="s">
         <v>173</v>
       </c>
-      <c r="C15" s="22" t="s">
+      <c r="C15" s="18" t="s">
         <v>174</v>
       </c>
-      <c r="D15" s="22" t="s">
+      <c r="D15" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="E15" s="22" t="s">
+      <c r="E15" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="F15" s="22" t="s">
+      <c r="F15" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="G15" s="22" t="s">
+      <c r="G15" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="H15" s="22" t="s">
+      <c r="H15" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="I15" s="22">
+      <c r="I15" s="18">
         <v>200</v>
       </c>
-      <c r="J15" s="22">
+      <c r="J15" s="18">
         <v>200</v>
       </c>
-      <c r="K15" s="24" t="s">
+      <c r="K15" s="20" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="60" x14ac:dyDescent="0.3">
-      <c r="A16" s="22" t="s">
+      <c r="A16" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="B16" s="22" t="s">
+      <c r="B16" s="18" t="s">
         <v>175</v>
       </c>
-      <c r="C16" s="22" t="s">
+      <c r="C16" s="18" t="s">
         <v>176</v>
       </c>
-      <c r="D16" s="22" t="s">
+      <c r="D16" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="E16" s="22" t="s">
+      <c r="E16" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="F16" s="22" t="s">
+      <c r="F16" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="G16" s="22" t="s">
+      <c r="G16" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="H16" s="22" t="s">
+      <c r="H16" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="I16" s="22">
+      <c r="I16" s="18">
         <v>403</v>
       </c>
-      <c r="J16" s="22">
+      <c r="J16" s="18">
         <v>403</v>
       </c>
-      <c r="K16" s="24" t="s">
+      <c r="K16" s="20" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="90" x14ac:dyDescent="0.3">
-      <c r="A17" s="22" t="s">
+      <c r="A17" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="B17" s="22" t="s">
+      <c r="B17" s="18" t="s">
         <v>177</v>
       </c>
-      <c r="C17" s="22" t="s">
+      <c r="C17" s="18" t="s">
         <v>178</v>
       </c>
-      <c r="D17" s="22" t="s">
+      <c r="D17" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="E17" s="22" t="s">
+      <c r="E17" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="F17" s="22" t="s">
+      <c r="F17" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="G17" s="22" t="s">
+      <c r="G17" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="H17" s="22" t="s">
+      <c r="H17" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="I17" s="22">
+      <c r="I17" s="18">
         <v>403</v>
       </c>
-      <c r="J17" s="22">
+      <c r="J17" s="18">
         <v>403</v>
       </c>
-      <c r="K17" s="24" t="s">
+      <c r="K17" s="20" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="30" x14ac:dyDescent="0.3">
-      <c r="A18" s="22" t="s">
+      <c r="A18" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="B18" s="22" t="s">
+      <c r="B18" s="18" t="s">
         <v>179</v>
       </c>
-      <c r="C18" s="22" t="s">
+      <c r="C18" s="18" t="s">
         <v>180</v>
       </c>
-      <c r="D18" s="22" t="s">
+      <c r="D18" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="E18" s="22" t="s">
+      <c r="E18" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="F18" s="22" t="s">
+      <c r="F18" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="G18" s="22" t="s">
+      <c r="G18" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="H18" s="22" t="s">
+      <c r="H18" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="I18" s="22">
+      <c r="I18" s="18">
         <v>403</v>
       </c>
-      <c r="J18" s="22">
+      <c r="J18" s="18">
         <v>403</v>
       </c>
-      <c r="K18" s="24" t="s">
+      <c r="K18" s="20" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="75" x14ac:dyDescent="0.3">
-      <c r="A19" s="22" t="s">
+      <c r="A19" s="18" t="s">
         <v>78</v>
       </c>
-      <c r="B19" s="22" t="s">
+      <c r="B19" s="18" t="s">
         <v>252</v>
       </c>
-      <c r="C19" s="22" t="s">
+      <c r="C19" s="18" t="s">
         <v>181</v>
       </c>
-      <c r="D19" s="22" t="s">
+      <c r="D19" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="E19" s="22" t="s">
+      <c r="E19" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="F19" s="22" t="s">
+      <c r="F19" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="G19" s="22" t="s">
+      <c r="G19" s="18" t="s">
         <v>65</v>
       </c>
-      <c r="H19" s="22" t="s">
+      <c r="H19" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="I19" s="22">
+      <c r="I19" s="18">
         <v>200</v>
       </c>
-      <c r="J19" s="22">
+      <c r="J19" s="18">
         <v>200</v>
       </c>
-      <c r="K19" s="24" t="s">
+      <c r="K19" s="20" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="30" x14ac:dyDescent="0.3">
-      <c r="A20" s="22" t="s">
+      <c r="A20" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="B20" s="22" t="s">
+      <c r="B20" s="18" t="s">
         <v>253</v>
       </c>
-      <c r="C20" s="22" t="s">
+      <c r="C20" s="18" t="s">
         <v>182</v>
       </c>
-      <c r="D20" s="22" t="s">
+      <c r="D20" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="E20" s="22" t="s">
+      <c r="E20" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="F20" s="22" t="s">
+      <c r="F20" s="18" t="s">
         <v>254</v>
       </c>
-      <c r="G20" s="22" t="s">
+      <c r="G20" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="H20" s="22" t="s">
+      <c r="H20" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="I20" s="22">
+      <c r="I20" s="18">
         <v>200</v>
       </c>
-      <c r="J20" s="22">
+      <c r="J20" s="18">
         <v>200</v>
       </c>
-      <c r="K20" s="24" t="s">
+      <c r="K20" s="20" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="60" x14ac:dyDescent="0.3">
-      <c r="A21" s="22" t="s">
+      <c r="A21" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="B21" s="22" t="s">
+      <c r="B21" s="18" t="s">
         <v>183</v>
       </c>
-      <c r="C21" s="22" t="s">
+      <c r="C21" s="18" t="s">
         <v>184</v>
       </c>
-      <c r="D21" s="22" t="s">
+      <c r="D21" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="E21" s="22" t="s">
+      <c r="E21" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="F21" s="22" t="s">
+      <c r="F21" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="G21" s="22" t="s">
+      <c r="G21" s="18" t="s">
         <v>48</v>
       </c>
-      <c r="H21" s="22" t="s">
+      <c r="H21" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="I21" s="22">
+      <c r="I21" s="18">
         <v>200</v>
       </c>
-      <c r="J21" s="22">
+      <c r="J21" s="18">
         <v>200</v>
       </c>
-      <c r="K21" s="24" t="s">
+      <c r="K21" s="20" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="90" x14ac:dyDescent="0.3">
-      <c r="A22" s="22" t="s">
+      <c r="A22" s="18" t="s">
         <v>83</v>
       </c>
-      <c r="B22" s="22" t="s">
+      <c r="B22" s="18" t="s">
         <v>177</v>
       </c>
-      <c r="C22" s="22" t="s">
+      <c r="C22" s="18" t="s">
         <v>185</v>
       </c>
-      <c r="D22" s="22" t="s">
+      <c r="D22" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="E22" s="22" t="s">
+      <c r="E22" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="F22" s="22" t="s">
+      <c r="F22" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="G22" s="22" t="s">
+      <c r="G22" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="H22" s="22" t="s">
+      <c r="H22" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="I22" s="22">
+      <c r="I22" s="18">
         <v>200</v>
       </c>
-      <c r="J22" s="22">
+      <c r="J22" s="18">
         <v>200</v>
       </c>
-      <c r="K22" s="24" t="s">
+      <c r="K22" s="20" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="30" x14ac:dyDescent="0.3">
-      <c r="A23" s="22" t="s">
+      <c r="A23" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="B23" s="22" t="s">
+      <c r="B23" s="18" t="s">
         <v>179</v>
       </c>
-      <c r="C23" s="22" t="s">
+      <c r="C23" s="18" t="s">
         <v>186</v>
       </c>
-      <c r="D23" s="22" t="s">
+      <c r="D23" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="E23" s="22" t="s">
+      <c r="E23" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="F23" s="22" t="s">
+      <c r="F23" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="G23" s="22" t="s">
+      <c r="G23" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="H23" s="22" t="s">
+      <c r="H23" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="I23" s="22">
+      <c r="I23" s="18">
         <v>403</v>
       </c>
-      <c r="J23" s="22">
+      <c r="J23" s="18">
         <v>403</v>
       </c>
-      <c r="K23" s="24" t="s">
+      <c r="K23" s="20" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="75" x14ac:dyDescent="0.3">
-      <c r="A24" s="22" t="s">
+      <c r="A24" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="B24" s="22" t="s">
+      <c r="B24" s="18" t="s">
         <v>173</v>
       </c>
-      <c r="C24" s="22" t="s">
+      <c r="C24" s="18" t="s">
         <v>187</v>
       </c>
-      <c r="D24" s="22" t="s">
+      <c r="D24" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="E24" s="22" t="s">
+      <c r="E24" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="F24" s="22" t="s">
+      <c r="F24" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="G24" s="22" t="s">
+      <c r="G24" s="18" t="s">
         <v>54</v>
       </c>
-      <c r="H24" s="22" t="s">
+      <c r="H24" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="I24" s="22">
+      <c r="I24" s="18">
         <v>200</v>
       </c>
-      <c r="J24" s="22">
+      <c r="J24" s="18">
         <v>200</v>
       </c>
-      <c r="K24" s="24" t="s">
+      <c r="K24" s="20" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="75" x14ac:dyDescent="0.3">
-      <c r="A25" s="22" t="s">
+      <c r="A25" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="B25" s="22" t="s">
+      <c r="B25" s="18" t="s">
         <v>255</v>
       </c>
-      <c r="C25" s="22" t="s">
+      <c r="C25" s="18" t="s">
         <v>188</v>
       </c>
-      <c r="D25" s="22" t="s">
+      <c r="D25" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="E25" s="22" t="s">
+      <c r="E25" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="F25" s="22" t="s">
+      <c r="F25" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="G25" s="22" t="s">
+      <c r="G25" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="H25" s="22" t="s">
+      <c r="H25" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="I25" s="22">
+      <c r="I25" s="18">
         <v>200</v>
       </c>
-      <c r="J25" s="22">
+      <c r="J25" s="18">
         <v>200</v>
       </c>
-      <c r="K25" s="24" t="s">
+      <c r="K25" s="20" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="60" x14ac:dyDescent="0.3">
-      <c r="A26" s="23" t="s">
+      <c r="A26" s="19" t="s">
         <v>256</v>
       </c>
-      <c r="B26" s="23" t="s">
+      <c r="B26" s="19" t="s">
         <v>248</v>
       </c>
-      <c r="C26" s="23" t="s">
+      <c r="C26" s="19" t="s">
         <v>257</v>
       </c>
-      <c r="D26" s="23" t="s">
+      <c r="D26" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="E26" s="23" t="s">
+      <c r="E26" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="F26" s="23" t="s">
+      <c r="F26" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="G26" s="23" t="s">
+      <c r="G26" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="H26" s="23" t="s">
+      <c r="H26" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="I26" s="23">
+      <c r="I26" s="19">
         <v>403</v>
       </c>
-      <c r="J26" s="23">
+      <c r="J26" s="19">
         <v>403</v>
       </c>
-      <c r="K26" s="24" t="s">
+      <c r="K26" s="20" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="75" x14ac:dyDescent="0.3">
-      <c r="A27" s="23" t="s">
+      <c r="A27" s="19" t="s">
         <v>258</v>
       </c>
-      <c r="B27" s="23" t="s">
+      <c r="B27" s="19" t="s">
         <v>160</v>
       </c>
-      <c r="C27" s="23" t="s">
+      <c r="C27" s="19" t="s">
         <v>259</v>
       </c>
-      <c r="D27" s="23" t="s">
+      <c r="D27" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="E27" s="23" t="s">
+      <c r="E27" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="F27" s="23" t="s">
+      <c r="F27" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="G27" s="23" t="s">
+      <c r="G27" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="H27" s="23" t="s">
+      <c r="H27" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="I27" s="23">
+      <c r="I27" s="19">
         <v>401</v>
       </c>
-      <c r="J27" s="23">
+      <c r="J27" s="19">
         <v>401</v>
       </c>
-      <c r="K27" s="24" t="s">
+      <c r="K27" s="20" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="90" x14ac:dyDescent="0.3">
-      <c r="A28" s="23" t="s">
+      <c r="A28" s="19" t="s">
         <v>260</v>
       </c>
-      <c r="B28" s="23" t="s">
+      <c r="B28" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="C28" s="23" t="s">
+      <c r="C28" s="19" t="s">
         <v>261</v>
       </c>
-      <c r="D28" s="23" t="s">
+      <c r="D28" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="E28" s="23" t="s">
+      <c r="E28" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="F28" s="23" t="s">
+      <c r="F28" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="G28" s="23" t="s">
+      <c r="G28" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="H28" s="23" t="s">
+      <c r="H28" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="I28" s="23">
+      <c r="I28" s="19">
         <v>401</v>
       </c>
-      <c r="J28" s="23">
+      <c r="J28" s="19">
         <v>401</v>
       </c>
-      <c r="K28" s="24" t="s">
+      <c r="K28" s="20" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="45" x14ac:dyDescent="0.3">
-      <c r="A29" s="23" t="s">
+      <c r="A29" s="19" t="s">
         <v>239</v>
       </c>
-      <c r="B29" s="23" t="s">
+      <c r="B29" s="19" t="s">
         <v>262</v>
       </c>
-      <c r="C29" s="23" t="s">
+      <c r="C29" s="19" t="s">
         <v>263</v>
       </c>
-      <c r="D29" s="23" t="s">
+      <c r="D29" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="E29" s="23" t="s">
+      <c r="E29" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="F29" s="23" t="s">
+      <c r="F29" s="19" t="s">
         <v>264</v>
       </c>
-      <c r="G29" s="23" t="s">
+      <c r="G29" s="19" t="s">
         <v>265</v>
       </c>
-      <c r="H29" s="23" t="s">
+      <c r="H29" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="I29" s="23">
+      <c r="I29" s="19">
         <v>200</v>
       </c>
-      <c r="J29" s="23">
+      <c r="J29" s="19">
         <v>200</v>
       </c>
-      <c r="K29" s="24" t="s">
+      <c r="K29" s="20" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="75" x14ac:dyDescent="0.3">
-      <c r="A30" s="23" t="s">
+      <c r="A30" s="19" t="s">
         <v>238</v>
       </c>
-      <c r="B30" s="23" t="s">
+      <c r="B30" s="19" t="s">
         <v>266</v>
       </c>
-      <c r="C30" s="23" t="s">
+      <c r="C30" s="19" t="s">
         <v>267</v>
       </c>
-      <c r="D30" s="23" t="s">
+      <c r="D30" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="E30" s="23" t="s">
+      <c r="E30" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="F30" s="23" t="s">
+      <c r="F30" s="19" t="s">
         <v>268</v>
       </c>
-      <c r="G30" s="23" t="s">
+      <c r="G30" s="19" t="s">
         <v>269</v>
       </c>
-      <c r="H30" s="23" t="s">
+      <c r="H30" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="I30" s="23">
+      <c r="I30" s="19">
         <v>400</v>
       </c>
-      <c r="J30" s="23">
+      <c r="J30" s="19">
         <v>400</v>
       </c>
-      <c r="K30" s="24" t="s">
+      <c r="K30" s="20" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="30" x14ac:dyDescent="0.3">
-      <c r="A31" s="23" t="s">
+      <c r="A31" s="19" t="s">
         <v>228</v>
       </c>
-      <c r="B31" s="23" t="s">
+      <c r="B31" s="19" t="s">
         <v>270</v>
       </c>
-      <c r="C31" s="23" t="s">
+      <c r="C31" s="19" t="s">
         <v>271</v>
       </c>
-      <c r="D31" s="23" t="s">
+      <c r="D31" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="E31" s="23" t="s">
+      <c r="E31" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="F31" s="23" t="s">
+      <c r="F31" s="19" t="s">
         <v>254</v>
       </c>
-      <c r="G31" s="23" t="s">
+      <c r="G31" s="19" t="s">
         <v>80</v>
       </c>
-      <c r="H31" s="23" t="s">
+      <c r="H31" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="I31" s="23">
+      <c r="I31" s="19">
         <v>401</v>
       </c>
-      <c r="J31" s="23">
+      <c r="J31" s="19">
         <v>401</v>
       </c>
-      <c r="K31" s="24" t="s">
+      <c r="K31" s="20" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="32" spans="1:11" ht="75" x14ac:dyDescent="0.3">
-      <c r="A32" s="23" t="s">
+      <c r="A32" s="19" t="s">
         <v>272</v>
       </c>
-      <c r="B32" s="23" t="s">
+      <c r="B32" s="19" t="s">
         <v>167</v>
       </c>
-      <c r="C32" s="23" t="s">
+      <c r="C32" s="19" t="s">
         <v>273</v>
       </c>
-      <c r="D32" s="23" t="s">
+      <c r="D32" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="E32" s="23" t="s">
+      <c r="E32" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="F32" s="23" t="s">
+      <c r="F32" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="G32" s="23" t="s">
+      <c r="G32" s="19" t="s">
         <v>274</v>
       </c>
-      <c r="H32" s="23" t="s">
+      <c r="H32" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="I32" s="23">
+      <c r="I32" s="19">
         <v>401</v>
       </c>
-      <c r="J32" s="23">
+      <c r="J32" s="19">
         <v>401</v>
       </c>
-      <c r="K32" s="24" t="s">
+      <c r="K32" s="20" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="33" spans="1:11" ht="45" x14ac:dyDescent="0.3">
-      <c r="A33" s="23" t="s">
+      <c r="A33" s="19" t="s">
         <v>275</v>
       </c>
-      <c r="B33" s="23" t="s">
+      <c r="B33" s="19" t="s">
         <v>276</v>
       </c>
-      <c r="C33" s="23" t="s">
+      <c r="C33" s="19" t="s">
         <v>277</v>
       </c>
-      <c r="D33" s="23" t="s">
+      <c r="D33" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="E33" s="23" t="s">
+      <c r="E33" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="F33" s="23" t="s">
+      <c r="F33" s="19" t="s">
         <v>278</v>
       </c>
-      <c r="G33" s="23" t="s">
+      <c r="G33" s="19" t="s">
         <v>279</v>
       </c>
-      <c r="H33" s="23" t="s">
+      <c r="H33" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="I33" s="23">
+      <c r="I33" s="19">
         <v>200</v>
       </c>
-      <c r="J33" s="23">
+      <c r="J33" s="19">
         <v>200</v>
       </c>
-      <c r="K33" s="24" t="s">
+      <c r="K33" s="20" t="s">
         <v>44</v>
       </c>
     </row>

--- a/Docs/QA-Testing/Test_Case_DecisionTable.xlsx
+++ b/Docs/QA-Testing/Test_Case_DecisionTable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10909"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\KiemChungPhanMem\Docs\QA-Testing\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/admin/Downloads/Online-Store/Docs/QA-Testing/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2C9F1F4-CD03-4268-B51F-67F470E1C921}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A0F0F6A5-0E80-431E-B2E3-D0E2E288BE2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="33600" windowHeight="21000" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="00_Huong_Dan_6_Buoc" sheetId="1" r:id="rId1"/>
@@ -1353,12 +1353,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="23" t="s">
         <v>91</v>
       </c>
@@ -1369,7 +1369,7 @@
       <c r="F1" s="24"/>
       <c r="G1" s="24"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -1378,13 +1378,13 @@
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
     </row>
-    <row r="3" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="22" t="s">
         <v>94</v>
       </c>
       <c r="B3" s="22"/>
     </row>
-    <row r="4" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="21" t="s">
         <v>93</v>
       </c>
@@ -1393,7 +1393,7 @@
       <c r="D4" s="21"/>
       <c r="E4" s="21"/>
     </row>
-    <row r="5" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="21" t="s">
         <v>96</v>
       </c>
@@ -1402,7 +1402,7 @@
       <c r="D5" s="21"/>
       <c r="E5" s="21"/>
     </row>
-    <row r="6" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="21" t="s">
         <v>95</v>
       </c>
@@ -1410,20 +1410,20 @@
       <c r="C6" s="21"/>
       <c r="D6" s="21"/>
     </row>
-    <row r="7" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="11"/>
       <c r="B7" s="11"/>
       <c r="C7" s="11"/>
       <c r="D7" s="11"/>
     </row>
-    <row r="8" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="22" t="s">
         <v>97</v>
       </c>
       <c r="B8" s="22"/>
       <c r="C8" s="22"/>
     </row>
-    <row r="9" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="21" t="s">
         <v>98</v>
       </c>
@@ -1433,21 +1433,21 @@
       <c r="E9" s="21"/>
       <c r="F9" s="21"/>
     </row>
-    <row r="10" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="21" t="s">
         <v>99</v>
       </c>
       <c r="B10" s="21"/>
       <c r="C10" s="21"/>
     </row>
-    <row r="11" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="21" t="s">
         <v>100</v>
       </c>
       <c r="B11" s="21"/>
       <c r="C11" s="21"/>
     </row>
-    <row r="12" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="21" t="s">
         <v>101</v>
       </c>
@@ -1458,7 +1458,7 @@
       <c r="F12" s="21"/>
       <c r="G12" s="21"/>
     </row>
-    <row r="13" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="21" t="s">
         <v>102</v>
       </c>
@@ -1468,7 +1468,7 @@
       <c r="E13" s="21"/>
       <c r="F13" s="21"/>
     </row>
-    <row r="14" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="21" t="s">
         <v>103</v>
       </c>
@@ -1478,10 +1478,10 @@
       <c r="E14" s="21"/>
       <c r="F14" s="21"/>
     </row>
-    <row r="15" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15"/>
     </row>
-    <row r="16" spans="1:9" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="21" t="s">
         <v>92</v>
       </c>
@@ -1494,7 +1494,7 @@
       <c r="H16" s="21"/>
       <c r="I16" s="21"/>
     </row>
-    <row r="17" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="21" t="s">
         <v>104</v>
       </c>
@@ -1505,7 +1505,7 @@
       <c r="F17" s="21"/>
       <c r="G17" s="21"/>
     </row>
-    <row r="18" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="21" t="s">
         <v>105</v>
       </c>
@@ -1542,27 +1542,27 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:L19"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
-    <col min="2" max="2" width="10.21875" customWidth="1"/>
+    <col min="2" max="2" width="10.1640625" customWidth="1"/>
     <col min="3" max="3" width="9.6640625" customWidth="1"/>
-    <col min="4" max="4" width="9.88671875" customWidth="1"/>
-    <col min="5" max="5" width="10.21875" customWidth="1"/>
+    <col min="4" max="4" width="9.83203125" customWidth="1"/>
+    <col min="5" max="5" width="10.1640625" customWidth="1"/>
     <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="10.109375" customWidth="1"/>
+    <col min="7" max="7" width="10.1640625" customWidth="1"/>
     <col min="8" max="8" width="10.6640625" customWidth="1"/>
-    <col min="9" max="9" width="10.21875" customWidth="1"/>
-    <col min="10" max="10" width="10.77734375" customWidth="1"/>
+    <col min="9" max="9" width="10.1640625" customWidth="1"/>
+    <col min="10" max="10" width="10.83203125" customWidth="1"/>
     <col min="11" max="11" width="13.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="8"/>
       <c r="B2" s="8" t="s">
         <v>1</v>
@@ -1598,7 +1598,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="9" t="s">
         <v>109</v>
       </c>
@@ -1636,7 +1636,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="9" t="s">
         <v>112</v>
       </c>
@@ -1674,7 +1674,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="9" t="s">
         <v>113</v>
       </c>
@@ -1712,7 +1712,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="9" t="s">
         <v>118</v>
       </c>
@@ -1741,7 +1741,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="9" t="s">
         <v>119</v>
       </c>
@@ -1765,7 +1765,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="9" t="s">
         <v>120</v>
       </c>
@@ -1791,7 +1791,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" ht="48" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="s">
         <v>11</v>
       </c>
@@ -1829,12 +1829,12 @@
         <v>107</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="L10" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="14" t="s">
         <v>197</v>
       </c>
@@ -1844,7 +1844,7 @@
       <c r="E11" s="14"/>
       <c r="F11" s="14"/>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="4"/>
       <c r="B12" s="4" t="s">
         <v>18</v>
@@ -1865,7 +1865,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
         <v>109</v>
       </c>
@@ -1888,7 +1888,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
         <v>112</v>
       </c>
@@ -1911,7 +1911,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" ht="32" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
         <v>113</v>
       </c>
@@ -1934,7 +1934,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
         <v>118</v>
       </c>
@@ -1952,7 +1952,7 @@
       </c>
       <c r="F16" s="3"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
         <v>200</v>
       </c>
@@ -1964,7 +1964,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" ht="48" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
         <v>23</v>
       </c>
@@ -1984,7 +1984,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="19" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A19" s="15" t="s">
         <v>11</v>
       </c>
@@ -2013,17 +2013,17 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E20"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.109375" customWidth="1"/>
+    <col min="1" max="1" width="17.1640625" customWidth="1"/>
     <col min="2" max="2" width="12.33203125" customWidth="1"/>
-    <col min="3" max="3" width="13.44140625" customWidth="1"/>
-    <col min="4" max="4" width="11.88671875" customWidth="1"/>
-    <col min="5" max="5" width="10.5546875" customWidth="1"/>
+    <col min="3" max="3" width="13.5" customWidth="1"/>
+    <col min="4" max="4" width="11.83203125" customWidth="1"/>
+    <col min="5" max="5" width="10.5" customWidth="1"/>
     <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>216</v>
       </c>
@@ -2031,7 +2031,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="8"/>
       <c r="B2" s="8" t="s">
         <v>1</v>
@@ -2046,7 +2046,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="9" t="s">
         <v>109</v>
       </c>
@@ -2063,7 +2063,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="32" x14ac:dyDescent="0.2">
       <c r="A4" s="9" t="s">
         <v>112</v>
       </c>
@@ -2080,7 +2080,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="9" t="s">
         <v>113</v>
       </c>
@@ -2094,7 +2094,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="9" t="s">
         <v>118</v>
       </c>
@@ -2107,7 +2107,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="9" t="s">
         <v>119</v>
       </c>
@@ -2120,7 +2120,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="9" t="s">
         <v>120</v>
       </c>
@@ -2130,7 +2130,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" ht="32" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="s">
         <v>11</v>
       </c>
@@ -2147,12 +2147,12 @@
         <v>212</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="E10" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>217</v>
       </c>
@@ -2160,7 +2160,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="8"/>
       <c r="B12" s="8" t="s">
         <v>18</v>
@@ -2175,7 +2175,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="9" t="s">
         <v>109</v>
       </c>
@@ -2189,7 +2189,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" ht="32" x14ac:dyDescent="0.2">
       <c r="A14" s="9" t="s">
         <v>112</v>
       </c>
@@ -2203,7 +2203,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="9" t="s">
         <v>113</v>
       </c>
@@ -2217,7 +2217,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="9" t="s">
         <v>218</v>
       </c>
@@ -2227,7 +2227,7 @@
       <c r="C16" s="7"/>
       <c r="D16" s="7"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="9" t="s">
         <v>219</v>
       </c>
@@ -2237,7 +2237,7 @@
       </c>
       <c r="D17" s="10"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="9" t="s">
         <v>220</v>
       </c>
@@ -2247,7 +2247,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" ht="32" x14ac:dyDescent="0.2">
       <c r="A19" s="9" t="s">
         <v>23</v>
       </c>
@@ -2261,7 +2261,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="20" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" ht="32" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
         <v>11</v>
       </c>
@@ -2283,25 +2283,25 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:K22"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16.44140625" customWidth="1"/>
-    <col min="2" max="2" width="10.88671875" customWidth="1"/>
+    <col min="1" max="1" width="16.5" customWidth="1"/>
+    <col min="2" max="2" width="10.83203125" customWidth="1"/>
     <col min="3" max="3" width="12.33203125" customWidth="1"/>
     <col min="4" max="5" width="11.6640625" customWidth="1"/>
     <col min="6" max="6" width="11.33203125" customWidth="1"/>
     <col min="7" max="7" width="11" customWidth="1"/>
-    <col min="8" max="8" width="10.44140625" customWidth="1"/>
-    <col min="9" max="9" width="10.77734375" customWidth="1"/>
-    <col min="10" max="10" width="9.77734375" customWidth="1"/>
+    <col min="8" max="8" width="10.5" customWidth="1"/>
+    <col min="9" max="9" width="10.83203125" customWidth="1"/>
+    <col min="10" max="10" width="9.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="8"/>
       <c r="B2" s="8" t="s">
         <v>1</v>
@@ -2334,7 +2334,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="9" t="s">
         <v>109</v>
       </c>
@@ -2369,7 +2369,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="9" t="s">
         <v>112</v>
       </c>
@@ -2404,7 +2404,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="9" t="s">
         <v>128</v>
       </c>
@@ -2439,7 +2439,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A6" s="9" t="s">
         <v>129</v>
       </c>
@@ -2474,7 +2474,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="9" t="s">
         <v>118</v>
       </c>
@@ -2498,7 +2498,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="9" t="s">
         <v>119</v>
       </c>
@@ -2519,7 +2519,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A9" s="9" t="s">
         <v>120</v>
       </c>
@@ -2540,7 +2540,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A10" s="9" t="s">
         <v>11</v>
       </c>
@@ -2572,12 +2572,12 @@
         <v>135</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="K11" s="13" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>217</v>
       </c>
@@ -2585,7 +2585,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="8"/>
       <c r="B13" s="8" t="s">
         <v>18</v>
@@ -2606,7 +2606,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="9" t="s">
         <v>109</v>
       </c>
@@ -2629,7 +2629,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" ht="32" x14ac:dyDescent="0.2">
       <c r="A15" s="9" t="s">
         <v>112</v>
       </c>
@@ -2649,7 +2649,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="9" t="s">
         <v>128</v>
       </c>
@@ -2669,7 +2669,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A17" s="9" t="s">
         <v>129</v>
       </c>
@@ -2689,7 +2689,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A18" s="9" t="s">
         <v>218</v>
       </c>
@@ -2703,7 +2703,7 @@
       <c r="E18" s="10"/>
       <c r="F18" s="10"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A19" s="9" t="s">
         <v>219</v>
       </c>
@@ -2717,7 +2717,7 @@
       </c>
       <c r="F19" s="7"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" ht="16" x14ac:dyDescent="0.2">
       <c r="A20" s="9" t="s">
         <v>220</v>
       </c>
@@ -2729,7 +2729,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="21" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" ht="48" x14ac:dyDescent="0.2">
       <c r="A21" s="9" t="s">
         <v>23</v>
       </c>
@@ -2749,7 +2749,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="22" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" ht="32" x14ac:dyDescent="0.2">
       <c r="A22" s="15" t="s">
         <v>11</v>
       </c>
@@ -2777,23 +2777,23 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:H18"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16.5546875" customWidth="1"/>
-    <col min="2" max="2" width="13.88671875" customWidth="1"/>
+    <col min="1" max="1" width="16.5" customWidth="1"/>
+    <col min="2" max="2" width="13.83203125" customWidth="1"/>
     <col min="3" max="3" width="15.33203125" customWidth="1"/>
     <col min="4" max="4" width="18.33203125" customWidth="1"/>
     <col min="5" max="5" width="19" customWidth="1"/>
-    <col min="6" max="6" width="12.77734375" customWidth="1"/>
-    <col min="7" max="7" width="14.44140625" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" customWidth="1"/>
+    <col min="7" max="7" width="14.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="8"/>
       <c r="B2" s="8" t="s">
         <v>1</v>
@@ -2817,7 +2817,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="9" t="s">
         <v>109</v>
       </c>
@@ -2843,7 +2843,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A4" s="9" t="s">
         <v>138</v>
       </c>
@@ -2869,7 +2869,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A5" s="9" t="s">
         <v>113</v>
       </c>
@@ -2895,7 +2895,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A6" s="9" t="s">
         <v>118</v>
       </c>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="G6" s="7"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A7" s="9" t="s">
         <v>144</v>
       </c>
@@ -2932,7 +2932,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
@@ -2958,7 +2958,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>217</v>
       </c>
@@ -2966,7 +2966,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A11" s="8"/>
       <c r="B11" s="8" t="s">
         <v>18</v>
@@ -2981,7 +2981,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="9" t="s">
         <v>109</v>
       </c>
@@ -2996,7 +2996,7 @@
       </c>
       <c r="H12" s="16"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="9" t="s">
         <v>138</v>
       </c>
@@ -3013,7 +3013,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" ht="32" x14ac:dyDescent="0.2">
       <c r="A14" s="9" t="s">
         <v>113</v>
       </c>
@@ -3027,7 +3027,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="9" t="s">
         <v>219</v>
       </c>
@@ -3039,7 +3039,7 @@
       </c>
       <c r="D15" s="7"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A16" s="9" t="s">
         <v>240</v>
       </c>
@@ -3049,7 +3049,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" ht="16" x14ac:dyDescent="0.2">
       <c r="A17" s="9" t="s">
         <v>23</v>
       </c>
@@ -3063,7 +3063,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" ht="32" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
         <v>11</v>
       </c>
@@ -3086,21 +3086,21 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A59EFB8D-9E96-408A-B911-DD887A9C0092}">
   <dimension ref="A1:K33"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.109375" customWidth="1"/>
-    <col min="2" max="2" width="14.88671875" customWidth="1"/>
-    <col min="3" max="3" width="15.88671875" customWidth="1"/>
-    <col min="4" max="4" width="20.109375" customWidth="1"/>
-    <col min="5" max="5" width="12.109375" customWidth="1"/>
+    <col min="1" max="1" width="17.1640625" customWidth="1"/>
+    <col min="2" max="2" width="14.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="4" max="4" width="20.1640625" customWidth="1"/>
+    <col min="5" max="5" width="12.1640625" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
-    <col min="8" max="8" width="22.44140625" customWidth="1"/>
-    <col min="9" max="9" width="18.5546875" customWidth="1"/>
-    <col min="10" max="10" width="10.44140625" customWidth="1"/>
+    <col min="8" max="8" width="22.5" customWidth="1"/>
+    <col min="9" max="9" width="18.5" customWidth="1"/>
+    <col min="10" max="10" width="10.5" customWidth="1"/>
     <col min="11" max="11" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="34" x14ac:dyDescent="0.2">
       <c r="A1" s="17" t="s">
         <v>33</v>
       </c>
@@ -3135,7 +3135,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="45" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" ht="34" x14ac:dyDescent="0.2">
       <c r="A2" s="18" t="s">
         <v>40</v>
       </c>
@@ -3170,7 +3170,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="30" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:11" ht="34" x14ac:dyDescent="0.2">
       <c r="A3" s="18" t="s">
         <v>45</v>
       </c>
@@ -3205,7 +3205,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="60" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" ht="68" x14ac:dyDescent="0.2">
       <c r="A4" s="18" t="s">
         <v>47</v>
       </c>
@@ -3240,7 +3240,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="30" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" ht="34" x14ac:dyDescent="0.2">
       <c r="A5" s="18" t="s">
         <v>49</v>
       </c>
@@ -3275,7 +3275,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="45" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:11" ht="34" x14ac:dyDescent="0.2">
       <c r="A6" s="18" t="s">
         <v>51</v>
       </c>
@@ -3310,7 +3310,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="75" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:11" ht="85" x14ac:dyDescent="0.2">
       <c r="A7" s="18" t="s">
         <v>53</v>
       </c>
@@ -3345,7 +3345,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="45" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:11" ht="51" x14ac:dyDescent="0.2">
       <c r="A8" s="18" t="s">
         <v>55</v>
       </c>
@@ -3380,7 +3380,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="45" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:11" ht="51" x14ac:dyDescent="0.2">
       <c r="A9" s="18" t="s">
         <v>58</v>
       </c>
@@ -3415,7 +3415,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="60" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:11" ht="68" x14ac:dyDescent="0.2">
       <c r="A10" s="18" t="s">
         <v>60</v>
       </c>
@@ -3450,7 +3450,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="60" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:11" ht="68" x14ac:dyDescent="0.2">
       <c r="A11" s="18" t="s">
         <v>62</v>
       </c>
@@ -3485,7 +3485,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="75" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:11" ht="85" x14ac:dyDescent="0.2">
       <c r="A12" s="18" t="s">
         <v>64</v>
       </c>
@@ -3520,7 +3520,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="90" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:11" ht="85" x14ac:dyDescent="0.2">
       <c r="A13" s="18" t="s">
         <v>66</v>
       </c>
@@ -3555,7 +3555,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="14" spans="1:11" ht="75" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:11" ht="85" x14ac:dyDescent="0.2">
       <c r="A14" s="18" t="s">
         <v>68</v>
       </c>
@@ -3590,7 +3590,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="75" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:11" ht="85" x14ac:dyDescent="0.2">
       <c r="A15" s="18" t="s">
         <v>72</v>
       </c>
@@ -3625,7 +3625,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="60" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:11" ht="68" x14ac:dyDescent="0.2">
       <c r="A16" s="18" t="s">
         <v>74</v>
       </c>
@@ -3660,7 +3660,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="90" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:11" ht="102" x14ac:dyDescent="0.2">
       <c r="A17" s="18" t="s">
         <v>75</v>
       </c>
@@ -3695,7 +3695,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="1:11" ht="30" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:11" ht="34" x14ac:dyDescent="0.2">
       <c r="A18" s="18" t="s">
         <v>77</v>
       </c>
@@ -3730,7 +3730,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="19" spans="1:11" ht="75" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:11" ht="85" x14ac:dyDescent="0.2">
       <c r="A19" s="18" t="s">
         <v>78</v>
       </c>
@@ -3765,7 +3765,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="20" spans="1:11" ht="30" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:11" ht="34" x14ac:dyDescent="0.2">
       <c r="A20" s="18" t="s">
         <v>79</v>
       </c>
@@ -3800,7 +3800,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="21" spans="1:11" ht="60" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:11" ht="68" x14ac:dyDescent="0.2">
       <c r="A21" s="18" t="s">
         <v>81</v>
       </c>
@@ -3835,7 +3835,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="22" spans="1:11" ht="90" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:11" ht="102" x14ac:dyDescent="0.2">
       <c r="A22" s="18" t="s">
         <v>83</v>
       </c>
@@ -3870,7 +3870,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="30" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" ht="34" x14ac:dyDescent="0.2">
       <c r="A23" s="18" t="s">
         <v>84</v>
       </c>
@@ -3905,7 +3905,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="75" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" ht="85" x14ac:dyDescent="0.2">
       <c r="A24" s="18" t="s">
         <v>85</v>
       </c>
@@ -3940,7 +3940,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="75" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" ht="85" x14ac:dyDescent="0.2">
       <c r="A25" s="18" t="s">
         <v>86</v>
       </c>
@@ -3975,7 +3975,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="60" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" ht="68" x14ac:dyDescent="0.2">
       <c r="A26" s="19" t="s">
         <v>256</v>
       </c>
@@ -4010,7 +4010,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="75" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" ht="85" x14ac:dyDescent="0.2">
       <c r="A27" s="19" t="s">
         <v>258</v>
       </c>
@@ -4045,7 +4045,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="90" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" ht="102" x14ac:dyDescent="0.2">
       <c r="A28" s="19" t="s">
         <v>260</v>
       </c>
@@ -4080,7 +4080,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="45" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" ht="51" x14ac:dyDescent="0.2">
       <c r="A29" s="19" t="s">
         <v>239</v>
       </c>
@@ -4115,7 +4115,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="75" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:11" ht="85" x14ac:dyDescent="0.2">
       <c r="A30" s="19" t="s">
         <v>238</v>
       </c>
@@ -4150,7 +4150,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="30" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:11" ht="34" x14ac:dyDescent="0.2">
       <c r="A31" s="19" t="s">
         <v>228</v>
       </c>
@@ -4185,7 +4185,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="75" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:11" ht="85" x14ac:dyDescent="0.2">
       <c r="A32" s="19" t="s">
         <v>272</v>
       </c>
@@ -4220,7 +4220,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="33" spans="1:11" ht="45" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:11" ht="34" x14ac:dyDescent="0.2">
       <c r="A33" s="19" t="s">
         <v>275</v>
       </c>
